--- a/salon_forms/020_hair_extensions_service_contract--salon_forms.xlsx
+++ b/salon_forms/020_hair_extensions_service_contract--salon_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -869,8 +869,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -898,12 +898,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'salon',_'description':_'salon'}</t>
+          <t>salon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Salon', 'description': 'Salon'}</t>
+          <t>Salon</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'stylist',_'description':_'stylist'}</t>
+          <t>stylist</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Stylist', 'description': 'Stylist'}</t>
+          <t>Stylist</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'both',_'description':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Both', 'description': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'client',_'description':_'client'}</t>
+          <t>client</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Client', 'description': 'Client'}</t>
+          <t>Client</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_"client's_representative",_'description':_"client's_representative"}</t>
+          <t>client's_representative</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': "Client's Representative", 'description': "Client's Representative"}</t>
+          <t>Client's Representative</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'check',_'description':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Check', 'description': 'Check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'bank_transfer',_'description':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Bank Transfer', 'description': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'credit_card',_'description':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Credit Card', 'description': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'on_signing_of_contract',_'description':_'on_signing_of_contract'}</t>
+          <t>on_signing_of_contract</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'On Signing of Contract', 'description': 'On Signing of Contract'}</t>
+          <t>On Signing of Contract</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'on_completion_of_service',_'description':_'on_completion_of_service'}</t>
+          <t>on_completion_of_service</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'On Completion of Service', 'description': 'On Completion of Service'}</t>
+          <t>On Completion of Service</t>
         </is>
       </c>
     </row>
